--- a/My 3-Statement Model Visa.xlsx
+++ b/My 3-Statement Model Visa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ephra\OneDrive\Desktop\3-Statement Model Visa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073A34F6-F067-4438-B561-88ACB140DCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B215B7-903A-4699-A8B9-F36B288C4D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{964B22D8-42B5-47E9-A229-95F7D57B30E0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="104">
   <si>
     <t>Income Statement:</t>
   </si>
@@ -331,6 +331,27 @@
   </si>
   <si>
     <t>Increase (decrease) in cash, cash equivalents, restricted cash and restricted cash equivalents</t>
+  </si>
+  <si>
+    <t>Key Performance Metrics &amp; Drivers</t>
+  </si>
+  <si>
+    <t>Operating expenses</t>
+  </si>
+  <si>
+    <t>Diluted earnings per share</t>
+  </si>
+  <si>
+    <t>Non-GAAP operating expenses</t>
+  </si>
+  <si>
+    <t>Non-GAAP net income</t>
+  </si>
+  <si>
+    <t>Non-GAAP diluted earnings per share</t>
+  </si>
+  <si>
+    <t>Revenue Growth %</t>
   </si>
 </sst>
 </file>
@@ -454,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -471,7 +492,6 @@
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -523,6 +543,8 @@
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,25 +647,25 @@
       <sheetName val="SUBSIDIARIES"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
       <sheetData sheetId="19">
         <row r="17">
           <cell r="C17">
@@ -1056,10 +1078,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
       <sheetData sheetId="25">
         <row r="18">
           <cell r="C18">
@@ -1502,56 +1524,56 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
-      <sheetData sheetId="50"/>
-      <sheetData sheetId="51"/>
-      <sheetData sheetId="52"/>
-      <sheetData sheetId="53"/>
-      <sheetData sheetId="54"/>
-      <sheetData sheetId="55"/>
-      <sheetData sheetId="56"/>
-      <sheetData sheetId="57"/>
-      <sheetData sheetId="58"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61"/>
-      <sheetData sheetId="62"/>
-      <sheetData sheetId="63"/>
-      <sheetData sheetId="64"/>
-      <sheetData sheetId="65"/>
-      <sheetData sheetId="66"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69"/>
-      <sheetData sheetId="70"/>
-      <sheetData sheetId="71"/>
-      <sheetData sheetId="72"/>
-      <sheetData sheetId="73"/>
-      <sheetData sheetId="74"/>
-      <sheetData sheetId="75"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
+      <sheetData sheetId="36" refreshError="1"/>
+      <sheetData sheetId="37" refreshError="1"/>
+      <sheetData sheetId="38" refreshError="1"/>
+      <sheetData sheetId="39" refreshError="1"/>
+      <sheetData sheetId="40" refreshError="1"/>
+      <sheetData sheetId="41" refreshError="1"/>
+      <sheetData sheetId="42" refreshError="1"/>
+      <sheetData sheetId="43" refreshError="1"/>
+      <sheetData sheetId="44" refreshError="1"/>
+      <sheetData sheetId="45" refreshError="1"/>
+      <sheetData sheetId="46" refreshError="1"/>
+      <sheetData sheetId="47" refreshError="1"/>
+      <sheetData sheetId="48" refreshError="1"/>
+      <sheetData sheetId="49" refreshError="1"/>
+      <sheetData sheetId="50" refreshError="1"/>
+      <sheetData sheetId="51" refreshError="1"/>
+      <sheetData sheetId="52" refreshError="1"/>
+      <sheetData sheetId="53" refreshError="1"/>
+      <sheetData sheetId="54" refreshError="1"/>
+      <sheetData sheetId="55" refreshError="1"/>
+      <sheetData sheetId="56" refreshError="1"/>
+      <sheetData sheetId="57" refreshError="1"/>
+      <sheetData sheetId="58" refreshError="1"/>
+      <sheetData sheetId="59" refreshError="1"/>
+      <sheetData sheetId="60" refreshError="1"/>
+      <sheetData sheetId="61" refreshError="1"/>
+      <sheetData sheetId="62" refreshError="1"/>
+      <sheetData sheetId="63" refreshError="1"/>
+      <sheetData sheetId="64" refreshError="1"/>
+      <sheetData sheetId="65" refreshError="1"/>
+      <sheetData sheetId="66" refreshError="1"/>
+      <sheetData sheetId="67" refreshError="1"/>
+      <sheetData sheetId="68" refreshError="1"/>
+      <sheetData sheetId="69" refreshError="1"/>
+      <sheetData sheetId="70" refreshError="1"/>
+      <sheetData sheetId="71" refreshError="1"/>
+      <sheetData sheetId="72" refreshError="1"/>
+      <sheetData sheetId="73" refreshError="1"/>
+      <sheetData sheetId="74" refreshError="1"/>
+      <sheetData sheetId="75" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1643,26 +1665,26 @@
       <sheetName val="SUBSIDIARIES"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
       <sheetData sheetId="20">
         <row r="18">
           <cell r="C18">
@@ -1805,62 +1827,62 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
-      <sheetData sheetId="50"/>
-      <sheetData sheetId="51"/>
-      <sheetData sheetId="52"/>
-      <sheetData sheetId="53"/>
-      <sheetData sheetId="54"/>
-      <sheetData sheetId="55"/>
-      <sheetData sheetId="56"/>
-      <sheetData sheetId="57"/>
-      <sheetData sheetId="58"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61"/>
-      <sheetData sheetId="62"/>
-      <sheetData sheetId="63"/>
-      <sheetData sheetId="64"/>
-      <sheetData sheetId="65"/>
-      <sheetData sheetId="66"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69"/>
-      <sheetData sheetId="70"/>
-      <sheetData sheetId="71"/>
-      <sheetData sheetId="72"/>
-      <sheetData sheetId="73"/>
-      <sheetData sheetId="74"/>
-      <sheetData sheetId="75"/>
-      <sheetData sheetId="76"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
+      <sheetData sheetId="36" refreshError="1"/>
+      <sheetData sheetId="37" refreshError="1"/>
+      <sheetData sheetId="38" refreshError="1"/>
+      <sheetData sheetId="39" refreshError="1"/>
+      <sheetData sheetId="40" refreshError="1"/>
+      <sheetData sheetId="41" refreshError="1"/>
+      <sheetData sheetId="42" refreshError="1"/>
+      <sheetData sheetId="43" refreshError="1"/>
+      <sheetData sheetId="44" refreshError="1"/>
+      <sheetData sheetId="45" refreshError="1"/>
+      <sheetData sheetId="46" refreshError="1"/>
+      <sheetData sheetId="47" refreshError="1"/>
+      <sheetData sheetId="48" refreshError="1"/>
+      <sheetData sheetId="49" refreshError="1"/>
+      <sheetData sheetId="50" refreshError="1"/>
+      <sheetData sheetId="51" refreshError="1"/>
+      <sheetData sheetId="52" refreshError="1"/>
+      <sheetData sheetId="53" refreshError="1"/>
+      <sheetData sheetId="54" refreshError="1"/>
+      <sheetData sheetId="55" refreshError="1"/>
+      <sheetData sheetId="56" refreshError="1"/>
+      <sheetData sheetId="57" refreshError="1"/>
+      <sheetData sheetId="58" refreshError="1"/>
+      <sheetData sheetId="59" refreshError="1"/>
+      <sheetData sheetId="60" refreshError="1"/>
+      <sheetData sheetId="61" refreshError="1"/>
+      <sheetData sheetId="62" refreshError="1"/>
+      <sheetData sheetId="63" refreshError="1"/>
+      <sheetData sheetId="64" refreshError="1"/>
+      <sheetData sheetId="65" refreshError="1"/>
+      <sheetData sheetId="66" refreshError="1"/>
+      <sheetData sheetId="67" refreshError="1"/>
+      <sheetData sheetId="68" refreshError="1"/>
+      <sheetData sheetId="69" refreshError="1"/>
+      <sheetData sheetId="70" refreshError="1"/>
+      <sheetData sheetId="71" refreshError="1"/>
+      <sheetData sheetId="72" refreshError="1"/>
+      <sheetData sheetId="73" refreshError="1"/>
+      <sheetData sheetId="74" refreshError="1"/>
+      <sheetData sheetId="75" refreshError="1"/>
+      <sheetData sheetId="76" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2183,7 +2205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D331CDC-E640-4DD2-B051-E368A3962B8F}">
-  <dimension ref="B1:J101"/>
+  <dimension ref="B1:J111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -2192,21 +2214,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27" t="s">
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -2253,11 +2275,26 @@
         <f>[1]INCOME_STATEMENT!E18</f>
         <v>40000</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
+      <c r="F3" s="9">
+        <f>E3*(1+F104)</f>
+        <v>44000</v>
+      </c>
+      <c r="G3" s="9">
+        <f t="shared" ref="G3:J3" si="0">F3*(1+G104)</f>
+        <v>47960</v>
+      </c>
+      <c r="H3" s="9">
+        <f t="shared" si="0"/>
+        <v>51796.800000000003</v>
+      </c>
+      <c r="I3" s="9">
+        <f t="shared" si="0"/>
+        <v>55422.576000000008</v>
+      </c>
+      <c r="J3" s="9">
+        <f t="shared" si="0"/>
+        <v>58747.930560000015</v>
+      </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
@@ -2401,26 +2438,26 @@
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f>[1]INCOME_STATEMENT!C29</f>
         <v>21000</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>[1]INCOME_STATEMENT!D29</f>
         <v>23595</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <f>[1]INCOME_STATEMENT!E29</f>
         <v>23994</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
@@ -2513,26 +2550,26 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="15">
         <f>[1]INCOME_STATEMENT!C37</f>
         <v>17273</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <f>[1]INCOME_STATEMENT!D37</f>
         <v>19743</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <f>[1]INCOME_STATEMENT!E37</f>
         <v>20058</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
@@ -2586,7 +2623,7 @@
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="17" t="s">
         <v>57</v>
       </c>
       <c r="C25" s="7">
@@ -2603,7 +2640,7 @@
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="17" t="s">
         <v>35</v>
       </c>
       <c r="C26" s="7">
@@ -2620,7 +2657,7 @@
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="17" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="7">
@@ -2637,7 +2674,7 @@
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="17" t="s">
         <v>34</v>
       </c>
       <c r="C28" s="7">
@@ -2654,7 +2691,7 @@
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="17" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="7">
@@ -2671,7 +2708,7 @@
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="17" t="s">
         <v>38</v>
       </c>
       <c r="C30" s="7">
@@ -2688,7 +2725,7 @@
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="17" t="s">
         <v>39</v>
       </c>
       <c r="C31" s="7">
@@ -2705,7 +2742,7 @@
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="18" t="s">
         <v>40</v>
       </c>
       <c r="C32" s="7">
@@ -2722,7 +2759,7 @@
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="16" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="7">
@@ -2739,7 +2776,7 @@
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="16" t="s">
         <v>41</v>
       </c>
       <c r="C34" s="7">
@@ -2756,7 +2793,7 @@
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="7">
@@ -2773,7 +2810,7 @@
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="16" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="7">
@@ -2790,7 +2827,7 @@
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="16" t="s">
         <v>44</v>
       </c>
       <c r="C37" s="7">
@@ -2807,7 +2844,7 @@
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="16" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="7">
@@ -2824,34 +2861,34 @@
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="22">
         <f>[2]BALANCE_SHEET!C33</f>
         <v>90499</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="22">
         <f>[1]BALANCE_SHEET!C32</f>
         <v>94511</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="22">
         <f>[1]BALANCE_SHEET!D32</f>
         <v>99627</v>
       </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="17" t="s">
         <v>47</v>
       </c>
       <c r="C41" s="7">
@@ -2868,7 +2905,7 @@
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="17" t="s">
         <v>48</v>
       </c>
       <c r="C42" s="7">
@@ -2885,7 +2922,7 @@
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="17" t="s">
         <v>37</v>
       </c>
       <c r="C43" s="7">
@@ -2902,7 +2939,7 @@
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="17" t="s">
         <v>49</v>
       </c>
       <c r="C44" s="7">
@@ -2919,7 +2956,7 @@
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="17" t="s">
         <v>41</v>
       </c>
       <c r="C45" s="7">
@@ -2936,7 +2973,7 @@
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="17" t="s">
         <v>50</v>
       </c>
       <c r="C46" s="7">
@@ -2953,7 +2990,7 @@
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="17" t="s">
         <v>51</v>
       </c>
       <c r="C47" s="7">
@@ -2970,7 +3007,7 @@
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="17" t="s">
         <v>52</v>
       </c>
       <c r="C48" s="7">
@@ -2987,7 +3024,7 @@
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="17" t="s">
         <v>53</v>
       </c>
       <c r="C49" s="7">
@@ -3004,7 +3041,7 @@
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="17" t="s">
         <v>54</v>
       </c>
       <c r="C50" s="7">
@@ -3021,7 +3058,7 @@
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C51" s="7">
@@ -3038,7 +3075,7 @@
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="18" t="s">
+      <c r="B52" s="17" t="s">
         <v>56</v>
       </c>
       <c r="C52" s="7">
@@ -3055,26 +3092,26 @@
       </c>
     </row>
     <row r="53" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="15">
         <f>[2]BALANCE_SHEET!C47</f>
         <v>51766</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="15">
         <f>[1]BALANCE_SHEET!C46</f>
         <v>55374</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="15">
         <f>[1]BALANCE_SHEET!D46</f>
         <v>61718</v>
       </c>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
@@ -3106,34 +3143,34 @@
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="18" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="17" t="s">
+      <c r="B57" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C57" s="20">
+      <c r="C57" s="19">
         <f>[1]CASH_FLOW!C18</f>
         <v>17273</v>
       </c>
-      <c r="D57" s="20">
+      <c r="D57" s="19">
         <f>[1]CASH_FLOW!D18</f>
         <v>19743</v>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="19">
         <f>[1]CASH_FLOW!E18</f>
         <v>20058</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="16" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59" s="18" t="s">
+      <c r="B59" s="17" t="s">
         <v>41</v>
       </c>
       <c r="C59" s="7">
@@ -3150,7 +3187,7 @@
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="18" t="s">
+      <c r="B60" s="17" t="s">
         <v>61</v>
       </c>
       <c r="C60" s="7">
@@ -3167,7 +3204,7 @@
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B61" s="18" t="s">
+      <c r="B61" s="17" t="s">
         <v>20</v>
       </c>
       <c r="C61" s="7">
@@ -3184,7 +3221,7 @@
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="C62" s="7">
@@ -3201,7 +3238,7 @@
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="17" t="s">
         <v>63</v>
       </c>
       <c r="C63" s="7">
@@ -3218,7 +3255,7 @@
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="17" t="s">
         <v>64</v>
       </c>
       <c r="C64" s="7">
@@ -3235,7 +3272,7 @@
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="17" t="s">
         <v>65</v>
       </c>
       <c r="C65" s="7">
@@ -3252,12 +3289,12 @@
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B66" s="30" t="s">
+      <c r="B66" s="29" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="18" t="s">
+      <c r="B67" s="17" t="s">
         <v>36</v>
       </c>
       <c r="C67" s="7">
@@ -3274,7 +3311,7 @@
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B68" s="18" t="s">
+      <c r="B68" s="17" t="s">
         <v>34</v>
       </c>
       <c r="C68" s="7">
@@ -3291,7 +3328,7 @@
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B69" s="18" t="s">
+      <c r="B69" s="17" t="s">
         <v>41</v>
       </c>
       <c r="C69" s="7">
@@ -3308,7 +3345,7 @@
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B70" s="18" t="s">
+      <c r="B70" s="17" t="s">
         <v>45</v>
       </c>
       <c r="C70" s="7">
@@ -3325,7 +3362,7 @@
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B71" s="18" t="s">
+      <c r="B71" s="17" t="s">
         <v>47</v>
       </c>
       <c r="C71" s="7">
@@ -3342,7 +3379,7 @@
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B72" s="18" t="s">
+      <c r="B72" s="17" t="s">
         <v>48</v>
       </c>
       <c r="C72" s="7">
@@ -3359,7 +3396,7 @@
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B73" s="18" t="s">
+      <c r="B73" s="17" t="s">
         <v>67</v>
       </c>
       <c r="C73" s="7">
@@ -3376,7 +3413,7 @@
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B74" s="18" t="s">
+      <c r="B74" s="17" t="s">
         <v>52</v>
       </c>
       <c r="C74" s="7">
@@ -3393,34 +3430,34 @@
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="11">
         <f>[1]CASH_FLOW!C37</f>
         <v>20755</v>
       </c>
-      <c r="D75" s="12">
+      <c r="D75" s="11">
         <f>[1]CASH_FLOW!D37</f>
         <v>19950</v>
       </c>
-      <c r="E75" s="12">
+      <c r="E75" s="11">
         <f>[1]CASH_FLOW!E37</f>
         <v>23059</v>
       </c>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="12"/>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B76" s="19" t="s">
+      <c r="B76" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B77" s="18" t="s">
+      <c r="B77" s="17" t="s">
         <v>68</v>
       </c>
       <c r="C77" s="7">
@@ -3437,7 +3474,7 @@
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B78" s="18" t="s">
+      <c r="B78" s="17" t="s">
         <v>69</v>
       </c>
       <c r="C78" s="7">
@@ -3454,7 +3491,7 @@
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B79" s="18" t="s">
+      <c r="B79" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C79" s="7">
@@ -3471,24 +3508,24 @@
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B80" s="18" t="s">
+      <c r="B80" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C80" s="33">
+      <c r="C80" s="32">
         <f>[1]CASH_FLOW!C43</f>
         <v>0</v>
       </c>
-      <c r="D80" s="33">
+      <c r="D80" s="32">
         <f>[1]CASH_FLOW!D43</f>
         <v>-915</v>
       </c>
-      <c r="E80" s="33">
+      <c r="E80" s="32">
         <f>[1]CASH_FLOW!E43</f>
         <v>-887</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B81" s="18" t="s">
+      <c r="B81" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C81" s="7">
@@ -3505,7 +3542,7 @@
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B82" s="18" t="s">
+      <c r="B82" s="17" t="s">
         <v>73</v>
       </c>
       <c r="C82" s="7">
@@ -3522,7 +3559,7 @@
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B83" s="18" t="s">
+      <c r="B83" s="17" t="s">
         <v>74</v>
       </c>
       <c r="C83" s="7">
@@ -3539,34 +3576,34 @@
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B84" s="21" t="s">
+      <c r="B84" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C84" s="12">
+      <c r="C84" s="11">
         <f>[1]CASH_FLOW!C47</f>
         <v>-2006</v>
       </c>
-      <c r="D84" s="12">
+      <c r="D84" s="11">
         <f>[1]CASH_FLOW!D47</f>
         <v>-1926</v>
       </c>
-      <c r="E84" s="12">
+      <c r="E84" s="11">
         <f>[1]CASH_FLOW!E47</f>
         <v>708</v>
       </c>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="12"/>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B85" s="19" t="s">
+      <c r="B85" s="18" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B86" s="18" t="s">
+      <c r="B86" s="17" t="s">
         <v>75</v>
       </c>
       <c r="C86" s="7">
@@ -3583,7 +3620,7 @@
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B87" s="18" t="s">
+      <c r="B87" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C87" s="7">
@@ -3600,7 +3637,7 @@
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B88" s="18" t="s">
+      <c r="B88" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C88" s="7">
@@ -3617,24 +3654,24 @@
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B89" s="18" t="s">
+      <c r="B89" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C89" s="33">
+      <c r="C89" s="32">
         <f>[1]CASH_FLOW!C52</f>
         <v>0</v>
       </c>
-      <c r="D89" s="33">
+      <c r="D89" s="32">
         <f>[1]CASH_FLOW!D52</f>
         <v>0</v>
       </c>
-      <c r="E89" s="33">
+      <c r="E89" s="32">
         <f>[1]CASH_FLOW!E52</f>
         <v>3924</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B90" s="18" t="s">
+      <c r="B90" s="17" t="s">
         <v>79</v>
       </c>
       <c r="C90" s="7">
@@ -3651,7 +3688,7 @@
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B91" s="18" t="s">
+      <c r="B91" s="17" t="s">
         <v>80</v>
       </c>
       <c r="C91" s="7">
@@ -3668,7 +3705,7 @@
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B92" s="18" t="s">
+      <c r="B92" s="17" t="s">
         <v>81</v>
       </c>
       <c r="C92" s="7">
@@ -3685,7 +3722,7 @@
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B93" s="18" t="s">
+      <c r="B93" s="17" t="s">
         <v>82</v>
       </c>
       <c r="C93" s="7">
@@ -3702,7 +3739,7 @@
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B94" s="18" t="s">
+      <c r="B94" s="17" t="s">
         <v>95</v>
       </c>
       <c r="C94" s="7">
@@ -3719,7 +3756,7 @@
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B95" s="18" t="s">
+      <c r="B95" s="17" t="s">
         <v>96</v>
       </c>
       <c r="C95" s="7">
@@ -3736,7 +3773,7 @@
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B96" s="29" t="s">
+      <c r="B96" s="28" t="s">
         <v>93</v>
       </c>
       <c r="C96" s="7">
@@ -3753,87 +3790,233 @@
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B97" s="31" t="s">
+      <c r="B97" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C97" s="23">
+      <c r="C97" s="22">
         <f>[1]CASH_FLOW!C64</f>
         <v>21990</v>
       </c>
-      <c r="D97" s="23">
+      <c r="D97" s="22">
         <f>[1]CASH_FLOW!D64</f>
         <v>19763</v>
       </c>
-      <c r="E97" s="23">
+      <c r="E97" s="22">
         <f>[1]CASH_FLOW!E64</f>
         <v>24987</v>
       </c>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
-      <c r="H97" s="13"/>
-      <c r="I97" s="13"/>
-      <c r="J97" s="13"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="12"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B98" s="19" t="s">
+      <c r="B98" s="18" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B99" s="18" t="s">
+      <c r="B99" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C99" s="20">
+      <c r="C99" s="19">
         <f>[1]CASH_FLOW!C66</f>
         <v>3433</v>
       </c>
-      <c r="D99" s="20">
+      <c r="D99" s="19">
         <f>[1]CASH_FLOW!D66</f>
         <v>5775</v>
       </c>
-      <c r="E99" s="20">
+      <c r="E99" s="19">
         <f>[1]CASH_FLOW!E66</f>
         <v>4541</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B100" s="18" t="s">
+      <c r="B100" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C100" s="20">
+      <c r="C100" s="19">
         <f>[1]CASH_FLOW!C67</f>
         <v>617</v>
       </c>
-      <c r="D100" s="20">
+      <c r="D100" s="19">
         <f>[1]CASH_FLOW!D67</f>
         <v>583</v>
       </c>
-      <c r="E100" s="20">
+      <c r="E100" s="19">
         <f>[1]CASH_FLOW!E67</f>
         <v>587</v>
       </c>
     </row>
     <row r="101" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="32" t="s">
+      <c r="B101" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="C101" s="16">
+      <c r="C101" s="15">
         <f>[1]CASH_FLOW!C68</f>
         <v>96</v>
       </c>
-      <c r="D101" s="16">
+      <c r="D101" s="15">
         <f>[1]CASH_FLOW!D68</f>
         <v>52</v>
       </c>
-      <c r="E101" s="16">
+      <c r="E101" s="15">
         <f>[1]CASH_FLOW!E68</f>
         <v>59</v>
       </c>
-      <c r="F101" s="15"/>
-      <c r="G101" s="15"/>
-      <c r="H101" s="15"/>
-      <c r="I101" s="15"/>
-      <c r="J101" s="15"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="14"/>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B103" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B104" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C104" s="33"/>
+      <c r="D104" s="34">
+        <f>D3/C3-1</f>
+        <v>0.10023581294214923</v>
+      </c>
+      <c r="E104" s="34">
+        <f>E3/D3-1</f>
+        <v>0.11339976618604908</v>
+      </c>
+      <c r="F104" s="34">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="G104" s="34">
+        <f>9%</f>
+        <v>0.09</v>
+      </c>
+      <c r="H104" s="34">
+        <f>8%</f>
+        <v>0.08</v>
+      </c>
+      <c r="I104" s="34">
+        <f>7%</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J104" s="34">
+        <f>6%</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B105" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D105" s="34">
+        <f>D12/C12-1</f>
+        <v>5.8182442289539171E-2</v>
+      </c>
+      <c r="E105" s="34">
+        <f>E12/D12-1</f>
+        <v>0.29802935690536048</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B106" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D106" s="34">
+        <f>14%</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E106" s="34">
+        <f>2%</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B107" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D107" s="34">
+        <f>17%</f>
+        <v>0.17</v>
+      </c>
+      <c r="E107" s="34">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B108" s="16"/>
+      <c r="D108" s="34"/>
+      <c r="E108" s="34"/>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B109" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D109" s="34">
+        <f>11%</f>
+        <v>0.11</v>
+      </c>
+      <c r="E109" s="34">
+        <f>11%</f>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B110" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D110" s="34">
+        <f>12%</f>
+        <v>0.12</v>
+      </c>
+      <c r="E110" s="34">
+        <f>11%</f>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B111" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D111" s="34">
+        <f>15%</f>
+        <v>0.15</v>
+      </c>
+      <c r="E111" s="34">
+        <f>14%</f>
+        <v>0.14000000000000001</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
